--- a/Réseaux/Page-d'adresse.xlsx
+++ b/Réseaux/Page-d'adresse.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\marchanta.SNIRW\PROJETS\Projet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\marchanta.SNIRW\PROJETS\Projet\Réseaux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C27268F-AA9E-44F9-BC3E-4F6864FE470E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DA611B-8040-446C-AF5D-E42DB113F6B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{10BDCBB6-FE4F-40BA-A093-109290A4C3B6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>IPv4</t>
   </si>
@@ -213,7 +213,13 @@
     <t>pi2-3</t>
   </si>
   <si>
-    <t>b8-27-eb-1d-05-d1</t>
+    <t>b8-27-eb-48-50-84</t>
+  </si>
+  <si>
+    <t>2c-cf-67-64-2a-d5</t>
+  </si>
+  <si>
+    <t>pc-p</t>
   </si>
 </sst>
 </file>
@@ -732,6 +738,9 @@
       <c r="G4" t="s">
         <v>13</v>
       </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
       <c r="I4" t="s">
         <v>30</v>
       </c>
@@ -748,6 +757,9 @@
       </c>
       <c r="G5" t="s">
         <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
